--- a/jogos_2025-03-03.xlsx
+++ b/jogos_2025-03-03.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.86</v>
+        <v>5.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.02</v>
+        <v>3.39</v>
       </c>
       <c r="N6" t="n">
-        <v>2.57</v>
+        <v>1.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
         <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI6" t="n">
         <v>3.75</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['3', '7', '69']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['24', '57']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45719.41666666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,20 +1288,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>2.89</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['52', '78', '90+4']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45719.41666666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.64</v>
+        <v>2.61</v>
       </c>
       <c r="M8" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>2.59</v>
       </c>
       <c r="O8" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['90+10']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['34']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45719.41666666666</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -1564,7 +1564,7 @@
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['3', '21']</t>
+          <t>['3', '7', '69']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['75', '90']</t>
+          <t>['24', '57']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45719.41666666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.61</v>
+        <v>1.89</v>
       </c>
       <c r="M10" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="N10" t="n">
-        <v>2.59</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.44</v>
       </c>
       <c r="S10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['90+10']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45719.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,23 +1804,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.37</v>
+        <v>1.64</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="N11" t="n">
-        <v>2.89</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="AI11" t="n">
         <v>1.44</v>
       </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['52', '78', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45719.41666666666</v>
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EGS Gafsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,25 +1959,25 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="O12" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
         <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S12" t="n">
         <v>2.15</v>
@@ -1992,50 +1992,50 @@
         <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD12" t="n">
         <v>1.57</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['15', '21', '81', '90+1']</t>
+          <t>['90+12']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45719.41666666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.39</v>
+        <v>3.52</v>
       </c>
       <c r="N14" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="P14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.25</v>
-      </c>
       <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.44</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.37</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '44', '75', '85']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="n">
         <v>1.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45719.41666666666</v>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>EGS Gafsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,25 +2346,25 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="P15" t="n">
         <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
         <v>2.15</v>
@@ -2379,50 +2379,50 @@
         <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
         <v>1.57</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['90+12']</t>
+          <t>['15', '21', '81', '90+1']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45719.41666666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="N16" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA16" t="n">
         <v>5.5</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['7', '44', '75', '85']</t>
+          <t>['3', '21']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>['75', '90']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45719.41666666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Akwa United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lobi Stars</t>
+          <t>Katsina United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,65 +2733,65 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45719.45833333334</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Akwa United</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Katsina United</t>
+          <t>Lobi Stars</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2851,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,65 +2862,65 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45719.45833333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.3</v>
+        <v>1.08</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>2.05</v>
+        <v>23</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>17</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T22" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.37</v>
+        <v>1.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.48</v>
+        <v>2.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['22', '19']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.25</v>
+        <v>1.11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.95</v>
+        <v>6.5</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45719.52083333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.94</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y23" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['22', '19']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['23', '45']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45719.52083333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.08</v>
+        <v>2.07</v>
       </c>
       <c r="M24" t="n">
-        <v>9.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>23</v>
+        <v>3.94</v>
       </c>
       <c r="O24" t="n">
-        <v>1.36</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA24" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>17</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AB24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC24" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
+          <t>['23', '45']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG24" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>5.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45719.52083333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,65 +3765,65 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>3.44</v>
       </c>
       <c r="M26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O26" t="n">
         <v>4.05</v>
       </c>
-      <c r="N26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.05</v>
-      </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
-        <v>3.68</v>
+        <v>2.71</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.88</v>
+        <v>3.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['23', '49', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="AH26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2.4</v>
       </c>
-      <c r="AI26" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>3.12</v>
+        <v>1.82</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45719.5625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="N27" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="X27" t="n">
-        <v>2.56</v>
+        <v>3.68</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
+          <t>['23', '49', '77']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG27" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45719.5625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.44</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.14</v>
+        <v>5.25</v>
       </c>
       <c r="O28" t="n">
-        <v>4.05</v>
+        <v>2.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="T28" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.36</v>
       </c>
-      <c r="X28" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45719.5625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>2</v>
       </c>
-      <c r="H37" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.58</v>
+        <v>1.34</v>
       </c>
       <c r="M37" t="n">
-        <v>3.26</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>2.66</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S37" t="n">
         <v>3.2</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.85</v>
       </c>
-      <c r="T37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.11</v>
+        <v>1.67</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['30', '90']</t>
+          <t>['2', '15', '75']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['5', '53']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.47</v>
+        <v>2.95</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.07</v>
+        <v>1.33</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45719.625</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
         <v>1</v>
       </c>
-      <c r="I38" t="n">
-        <v>2</v>
-      </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.34</v>
+        <v>2.58</v>
       </c>
       <c r="M38" t="n">
-        <v>4.9</v>
+        <v>3.26</v>
       </c>
       <c r="N38" t="n">
-        <v>8.300000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="O38" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="T38" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U38" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X38" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['30', '90']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['5', '53']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI38" t="n">
         <v>2.07</v>
       </c>
-      <c r="AD38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['2', '15', '75']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['71']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ38" t="n">
-        <v>3.7</v>
+        <v>1.91</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45719.625</v>
@@ -5803,16 +5803,16 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>2</v>
@@ -5821,7 +5821,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,22 +5829,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="O42" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
         <v>1.3</v>
@@ -5853,31 +5853,31 @@
         <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U42" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X42" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC42" t="n">
         <v>1.53</v>
@@ -5887,25 +5887,25 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['21', '40']</t>
+          <t>['68', '88']</t>
         </is>
       </c>
       <c r="AG42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.7</v>
       </c>
-      <c r="AH42" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI42" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45719.66666666666</v>
@@ -5932,109 +5932,109 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2</v>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>2.1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['68', '88']</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45719.66666666666</v>
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S44" t="n">
         <v>3.4</v>
       </c>
-      <c r="N44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="T44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['21', '40']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI44" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45719.66666666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.19</v>
+        <v>6.7</v>
       </c>
       <c r="M45" t="n">
-        <v>2.76</v>
+        <v>5.12</v>
       </c>
       <c r="N45" t="n">
-        <v>3.98</v>
+        <v>1.3</v>
       </c>
       <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA45" t="n">
         <v>2.88</v>
       </c>
-      <c r="P45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W45" t="n">
+      <c r="AB45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.6</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AD45" t="n">
         <v>2.1</v>
       </c>
-      <c r="Y45" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '30']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '55', '72']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45719.66666666666</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>6.7</v>
+        <v>2.19</v>
       </c>
       <c r="M46" t="n">
-        <v>5.12</v>
+        <v>2.76</v>
       </c>
       <c r="N46" t="n">
-        <v>1.3</v>
+        <v>3.98</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="P46" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="T46" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="U46" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W46" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="X46" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.77</v>
+        <v>2.89</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['17', '30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['33', '55', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.77</v>
+        <v>1.2</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45719.66666666666</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,16 +6577,16 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="M48" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>4.8</v>
+        <v>3.36</v>
       </c>
       <c r="O48" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="P48" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>2.4</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['49', '76']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>['72']</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>2.95</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45719.66666666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,16 +6706,16 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="N49" t="n">
-        <v>3.36</v>
+        <v>4.8</v>
       </c>
       <c r="O49" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="P49" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="T49" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U49" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="V49" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W49" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="X49" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.87</v>
+        <v>2.77</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="AA49" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['49', '76']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>2.95</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45719.66666666666</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,16 +6835,16 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -6861,65 +6861,65 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="M50" t="n">
-        <v>2.85</v>
+        <v>3.27</v>
       </c>
       <c r="N50" t="n">
-        <v>3.53</v>
+        <v>5.1</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="P50" t="n">
         <v>1.91</v>
       </c>
       <c r="Q50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T50" t="n">
         <v>4</v>
       </c>
-      <c r="R50" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X50" t="n">
         <v>2.25</v>
       </c>
-      <c r="T50" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.43</v>
-      </c>
       <c r="Y50" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AB50" t="n">
         <v>1.14</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['25', '68']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6928,16 +6928,16 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45719.6875</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,25 +7093,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,43 +7119,43 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="M52" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="N52" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q52" t="n">
         <v>4</v>
       </c>
-      <c r="O52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4.5</v>
-      </c>
       <c r="R52" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S52" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T52" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="U52" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V52" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W52" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="X52" t="n">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="Y52" t="n">
         <v>2.3</v>
@@ -7164,38 +7164,38 @@
         <v>1.5</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC52" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI52" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>['8', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ52" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45719.6875</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="M53" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="N53" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S53" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['8', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
         <v>1.22</v>
       </c>
-      <c r="V53" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>['25', '68']</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH53" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AI53" t="n">
         <v>1.57</v>
       </c>
       <c r="AJ53" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45719.6875</v>
@@ -7351,23 +7351,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>1</v>
       </c>
-      <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="M54" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="O54" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P54" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="R54" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="S54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y54" t="n">
         <v>2.15</v>
       </c>
-      <c r="T54" t="n">
+      <c r="Z54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA54" t="n">
         <v>3.8</v>
       </c>
-      <c r="U54" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>5.25</v>
-      </c>
       <c r="AB54" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['16', '67']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45719.69791666666</v>
@@ -7470,29 +7470,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
         <v>1</v>
-      </c>
-      <c r="H55" t="n">
-        <v>2</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.45</v>
+        <v>1.85</v>
       </c>
       <c r="M55" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X55" t="n">
         <v>2.88</v>
       </c>
-      <c r="N55" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="O55" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Y55" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AA55" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['16', '62']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45719.69791666666</v>
@@ -7609,16 +7609,16 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
@@ -7627,7 +7627,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="M56" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="N56" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="O56" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Q56" t="n">
         <v>4.1</v>
       </c>
       <c r="R56" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="S56" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="T56" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="U56" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="V56" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W56" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="X56" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AA56" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45719.69791666666</v>
@@ -7738,19 +7738,19 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
         <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.56</v>
+        <v>3.92</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N57" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T57" t="n">
         <v>2.7</v>
       </c>
-      <c r="O57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U57" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V57" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W57" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="X57" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['16', '67']</t>
+          <t>['38', '78']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AI57" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45719.69791666666</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7882,94 +7882,94 @@
         <v>1</v>
       </c>
       <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
         <v>1</v>
       </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.92</v>
+        <v>2.21</v>
       </c>
       <c r="M58" t="n">
-        <v>4.3</v>
+        <v>3.18</v>
       </c>
       <c r="N58" t="n">
-        <v>1.72</v>
+        <v>3.29</v>
       </c>
       <c r="O58" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="P58" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="R58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W58" t="n">
         <v>1.35</v>
       </c>
-      <c r="S58" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['47', '87']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
         <v>1.29</v>
       </c>
-      <c r="X58" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>['38', '78']</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>2</v>
-      </c>
       <c r="AH58" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="AI58" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45719.69791666666</v>
@@ -7986,35 +7986,35 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G59" t="n">
         <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.21</v>
+        <v>1.33</v>
       </c>
       <c r="M59" t="n">
-        <v>3.18</v>
+        <v>5.4</v>
       </c>
       <c r="N59" t="n">
-        <v>3.29</v>
+        <v>10</v>
       </c>
       <c r="O59" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="P59" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.9</v>
+        <v>9.5</v>
       </c>
       <c r="R59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X59" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB59" t="n">
         <v>1.4</v>
       </c>
-      <c r="S59" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T59" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X59" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC59" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['47', '87']</t>
+          <t>['72', '90']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AJ59" t="n">
-        <v>2.35</v>
+        <v>5.5</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45719.69791666666</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,25 +8125,25 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
         <v>2</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.33</v>
+        <v>3.45</v>
       </c>
       <c r="M60" t="n">
-        <v>5.4</v>
+        <v>2.88</v>
       </c>
       <c r="N60" t="n">
-        <v>10</v>
+        <v>2.31</v>
       </c>
       <c r="O60" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="P60" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>9.5</v>
+        <v>3.05</v>
       </c>
       <c r="R60" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="S60" t="n">
-        <v>3.25</v>
+        <v>2.21</v>
       </c>
       <c r="T60" t="n">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="U60" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="V60" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W60" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="X60" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="Z60" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['72', '90']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '62']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="AH60" t="n">
-        <v>3.6</v>
+        <v>1.29</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="AJ60" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45719.69791666666</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,109 +8641,109 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Newell's Old Boys</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>2</v>
       </c>
       <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
         <v>2</v>
       </c>
-      <c r="J64" t="n">
-        <v>1</v>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.09</v>
+        <v>1.93</v>
       </c>
       <c r="M64" t="n">
-        <v>3.01</v>
+        <v>3.16</v>
       </c>
       <c r="N64" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="O64" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>5</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T64" t="n">
         <v>3.75</v>
       </c>
-      <c r="P64" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R64" t="n">
+      <c r="U64" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X64" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z64" t="n">
         <v>1.5</v>
       </c>
-      <c r="S64" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T64" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X64" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z64" t="n">
+      <c r="AA64" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>['4', '45+1']</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI64" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA64" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>['6', '33']</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>['45+4', '78']</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ64" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45719.875</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,109 +8770,109 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Newell's Old Boys</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>2</v>
       </c>
       <c r="I65" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" t="n">
         <v>1</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P65" t="n">
         <v>2</v>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="M65" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N65" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O65" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="R65" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>['6', '33']</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>['45+4', '78']</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI65" t="n">
         <v>2.38</v>
       </c>
-      <c r="T65" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>['4', '45+1']</t>
-        </is>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ65" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45719.875</v>
